--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_element_info/lang_element_info__skill_description__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_element_info/lang_element_info__skill_description__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Toàn đội gây Sát Thương Dissociation tăng trong 12 giây. Resonator kích hoạt hiệu ứng sẽ nhận Resonance Energy.</t>
+          <t>Dissociation damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Khuếch Tán và Dissociation sẽ giảm Kháng Khuếch Tán của mục tiêu &lt;color=#1398ef&gt;30%&lt;/color&gt; trong &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
+          <t>Upon dealing Diffusion and Dissociation DMG, reduces the target's Diffusion RES. by &lt;color=#1398ef&gt;30%&lt;/color&gt; for &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Khi gây Aero DMG và Dissociation, giảm Aero RES của mục tiêu &lt;color=#1398ef&gt;30%&lt;/color&gt; trong &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
+          <t>Upon dealing Aerodynamic and Dissociation DMG, reduces the target's Aerodynamic RES. by &lt;color=#1398ef&gt;30%&lt;/color&gt; for &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Khi gây Sát Thương Conduction và Dissociation, giảm Kháng Conduction của mục tiêu &lt;color=#1398ef&gt;30%&lt;/color&gt; trong &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
+          <t>Upon dealing Conduction and Dissociation DMG, reduces the target's Conduction RES. by &lt;color=#1398ef&gt;30%&lt;/color&gt; for &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Dung Hợp và Dissociation sẽ giảm Kháng Dung Hợp của mục tiêu &lt;color=#1398ef&gt;30%&lt;/color&gt; trong &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
+          <t>Upon dealing Fusion and Dissociation DMG, reduces the target's Fusion RES. by &lt;color=#1398ef&gt;30%&lt;/color&gt; for &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Đông Cứng và Dissociation sẽ giảm Kháng Đông Cứng của mục tiêu &lt;color=#1398ef&gt;30%&lt;/color&gt; trong &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
+          <t>Upon dealing Frozen and Dissociation DMG, reduces the target's Frozen RES. by &lt;color=#1398ef&gt;30%&lt;/color&gt; for &lt;color=#1398ef&gt;10s&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Spectro DMG của toàn đội tăng trong 12 giây. Resonator kích hoạt hiệu ứng sẽ nhận được Resonance Energy.</t>
+          <t>Spectra damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Khi ở trong phạm vi ảnh hưởng trong &lt;color=#1398ef&gt;3s&lt;/color&gt;, hiệu ứng Aerodynamic đã gây trên mục tiêu sẽ được kích hoạt thành Super-Aerodynamic trong 12 giây. (Super-Aerodynamic: Giảm 40% Aero RES DMGdynamic của mục tiêu)</t>
+          <t>When within AoE for &lt;color=#1398ef&gt;3s&lt;/color&gt;, Aerodynamic already inflicted onto targets will be stimulated to Super-Aerodynamic for 12s. (Super-Aerodynamic: Reduce the target's Aerodynamic DMG reduction by 40%)</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Khi ở trong phạm vi ảnh hưởng trong &lt;color=#1398ef&gt;3s&lt;/color&gt;, hiệu ứng Conduction đã gây trên mục tiêu sẽ được kích hoạt thành Super-Conduction trong 12 giây. (Super-Conduction: Giảm 40% Kháng sát thương Conduction của mục tiêu)</t>
+          <t>When within AoE for &lt;color=#1398ef&gt;3s&lt;/color&gt;, Conduction already inflicted onto targets will be stimulated to Super-Conduction for 12s. (Super-Conduction: Reduce the target's Conduction DMG reduction by 40%)</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Khi ở trong phạm vi ảnh hưởng trong &lt;color=#1398ef&gt;3s&lt;/color&gt;, hiệu ứng Smelt đã gây trên mục tiêu sẽ được kích hoạt thành Super-Smelt trong 12 giây. (Super-Smelt: Giảm 40% Kháng sát thương Smelt của mục tiêu)</t>
+          <t>When within AoE for &lt;color=#1398ef&gt;3s&lt;/color&gt;, Smelt already inflicted onto targets will be stimulated to Super-Smelt for 12s. (Super-Smelt: Reduce the target's Smelt DMG reduction by 40%)</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khi ở trong phạm vi ảnh hưởng trong &lt;color=#1398ef&gt;3s&lt;/color&gt;, hiệu ứng Condensation đã gây trên mục tiêu sẽ được kích hoạt thành Super-Condensation trong 12 giây. (Super-Condensation: Giảm 40% Kháng sát thương Condensation của mục tiêu)</t>
+          <t>When within AoE for &lt;color=#1398ef&gt;3s&lt;/color&gt;, Condensation already inflicted onto targets will be stimulated to Super-Condensation for 12s. (Super-Smelt: Reduce the target's Condensation DMG reduction by 40%)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sát thương Pneuma của toàn đội tăng trong 12 giây. Nhân vật kích hoạt hiệu ứng sẽ nhận được Resonance Energy.</t>
+          <t>Pneuma damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Thu thập mục tiêu trong phạm vi ảnh hưởng, gây Sát Thương Conduction và áp dụng 2 lần Hiệu Ứng Giảm Phòng Ngự, sau đó tăng mạnh Thanh Âm của chúng. Mục tiêu trong phạm vi sẽ bị ảnh hưởng bởi Aerodynamic và Conduction trong 20 giây. (Aerodynamic: Giá trị cộng hưởng của mục tiêu tích lũy nhanh hơn. Conduction: Mục tiêu dễ bị gián đoạn bởi các đòn tấn công.)</t>
+          <t>Gathers targets with AoE, deals Conduction DMG and inflicts them with 2x DEF Down, before greatly increasing their Audio Bar. Targets within the AoE with be inflicted Aerodynamic and Conduction for 20 seconds. (Aerodynamic: Target's resonance value accumulates faster. Conduction: Target are easily interrupted by attacks.)</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Khu Vực Dung Nhiệt + Khí Động học và kéo mục tiêu, đồng thời gây Sát Thương Dung Nhiệt mỗi giây trong &lt;color=#1398ef&gt;5s&lt;/color&gt;. Mục tiêu trong phạm vi ảnh hưởng sẽ bị ảnh hưởng bởi Khí Động học và Nung Chảy trong 20 giây. (Khí Động học: Giá trị cộng hưởng của mục tiêu tích lũy nhanh hơn. Nung Chảy: Mục tiêu chịu Sát Thương theo thời gian.)</t>
+          <t>Deals Fusion + Aerodynamic AoE DMG and pulls the target, while dealing Fusion each second for &lt;color=#1398ef&gt;5s&lt;/color&gt;. Targets within the AoE with be inflicted Aerodynamic and Smelt for 20 seconds. (Aerodynamic: Target's resonance value accumulates faster. Smelt: Target takes DoT DMG.)</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Khu Vực Băng Giá + Khí Động học và kéo mục tiêu, sau đó đóng băng chúng. Mục tiêu trong phạm vi ảnh hưởng sẽ bị ảnh hưởng bởi Khí Động học và Băng Giá trong 20 giây. (Khí Động học: Giá trị cộng hưởng của mục tiêu tích lũy nhanh hơn. Băng Giá: Tốc độ di chuyển của mục tiêu bị giảm.)</t>
+          <t>Deals Frozen + Aerodynamic AoE DMG and pulls the target, before Freezing them. Targets within the AoE with be inflicted Aerodynamic and Frozen for 20 seconds. (Aerodynamic: Target's resonance value accumulates faster. Frozen: Target's movement speed is decreased.)</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sát thương xung kích của toàn đội tăng trong 12 giây. Resonator kích hoạt hiệu ứng sẽ nhận Resonance Energy.</t>
+          <t>Impulse damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Gây lượng lớn Sát Thương Nung Chảy + Conduction. Mục tiêu trong phạm vi ảnh hưởng sẽ bị ảnh hưởng bởi Conduction và Nung Chảy trong 20 giây. (Conduction: Mục tiêu dễ bị gián đoạn bởi các đòn tấn công. Nung Chảy: Mục tiêu chịu Sát Thương theo thời gian.)</t>
+          <t>Deals large amounts Smelt + Conduction DMG. Targets within the AoE with be inflicted Conduction and Smelt for 20 seconds. (Conduction: Target are easily interrupted by attacks.. Smelt: Target takes DoT DMG.)</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Gây lượng lớn Sát Thương Băng Giá + Conduction. Mục tiêu trong phạm vi ảnh hưởng sẽ bị ảnh hưởng bởi Conduction và Băng Giá trong 20 giây. (Conduction: Mục tiêu dễ bị gián đoạn bởi các đòn tấn công. Băng Giá: Tốc độ di chuyển của mục tiêu bị giảm.)</t>
+          <t>Deals large amounts Frozen + Conduction DMG. Targets within the AoE with be inflicted Conduction and Frozen for 20 seconds. (Conduction: Target are easily interrupted by attacks.. Frozen: Target's movement speed is decreased.)</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Fusion DMG của toàn đội tăng trong 12 giây. Nhân vật kích hoạt hiệu ứng sẽ nhận được Resonance Energy.</t>
+          <t>Fusion damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Gây lượng lớn Sát Thương Dung Nhiệt + Băng Giá. Mục tiêu trong phạm vi ảnh hưởng sẽ bị ảnh hưởng bởi Nung Chảy và Băng Giá trong 20 giây. (Nung Chảy: Mục tiêu chịu Sát Thương theo thời gian. Băng Giá: Tốc độ di chuyển của mục tiêu bị giảm.)</t>
+          <t>Deals large amounts Fusion + Frozen DMG. Targets within the AoE with be inflicted Smelt and Frozen for 20 seconds. (Smelt: Target takes DoT DMG. Frozen: Target's movement speed is decreased.)</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Glacio DMG của toàn đội tăng trong 12 giây. Resonator kích hoạt hiệu ứng sẽ nhận được Resonance Energy.</t>
+          <t>Glacio damage done by the whole team increase for 12 seconds. The character that triggers the effect gains resonance energy.</t>
         </is>
       </c>
     </row>
